--- a/docs/Files/Tutorial6_JV_2/ODYM_T6_P5_ToRefurbishment_V1.0.xlsx
+++ b/docs/Files/Tutorial6_JV_2/ODYM_T6_P5_ToRefurbishment_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EFCBAD-4CE4-46D4-BDC3-4B96F375878F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEC4B28-A842-4661-8A8C-EAE0DF1C0494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -191,9 +191,6 @@
     <t>Steel shred</t>
   </si>
   <si>
-    <t>ODYM_Classifications_Master_Tutorial6_MaTrace</t>
-  </si>
-  <si>
     <t>BAU</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>Made up; Landfill is .6; to used export is 0.01</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EVLIB</t>
   </si>
 </sst>
 </file>
@@ -794,15 +794,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="4" width="31.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>39</v>
       </c>
@@ -813,12 +813,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
@@ -827,12 +827,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -841,12 +841,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -855,7 +855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -869,7 +869,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -883,7 +883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -897,12 +897,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -911,12 +911,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -925,12 +925,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -939,7 +939,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -953,7 +953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -967,7 +967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
@@ -981,7 +981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
@@ -995,12 +995,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1009,37 +1009,37 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>2</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>10</v>
       </c>
@@ -1076,18 +1076,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -1096,18 +1096,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
         <v>71</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -1116,18 +1116,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
         <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -1136,12 +1136,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
         <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>14</v>
@@ -1156,7 +1156,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C27" s="8" t="s">
         <v>15</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
@@ -1180,32 +1180,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="4" max="4" width="24.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" customWidth="1"/>
+    <col min="10" max="10" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>11</v>
@@ -1223,12 +1223,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
@@ -1249,21 +1249,21 @@
         <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1278,21 +1278,21 @@
         <v>54</v>
       </c>
       <c r="I3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1307,15 +1307,15 @@
         <v>54</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -1336,15 +1336,15 @@
         <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
@@ -1365,21 +1365,21 @@
         <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1394,21 +1394,21 @@
         <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1423,15 +1423,15 @@
         <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
@@ -1452,13 +1452,13 @@
         <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D10" s="1"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F35" s="1"/>
     </row>
   </sheetData>
@@ -1470,47 +1470,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:M3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="13">
         <v>43344</v>
       </c>
@@ -1519,13 +1519,13 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
         <v>89</v>
-      </c>
-      <c r="H3" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1536,56 +1536,56 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>1</v>
